--- a/01-meridian-health-grc-program/artifacts/control_mapping_spreadsheet.xlsx
+++ b/01-meridian-health-grc-program/artifacts/control_mapping_spreadsheet.xlsx
@@ -10,7 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Control Mapping'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Control Mapping'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Legend'!$A$1:$B$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -510,7 +514,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1437,7 +1441,8 @@
       <formula>SEARCH("Implemented",G5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1445,7 +1450,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1510,6 +1515,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>